--- a/config/excel/CfgEnemySkills.xlsx
+++ b/config/excel/CfgEnemySkills.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemySkills" sheetId="1" r:id="R45cf268002c34851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemySkills" sheetId="1" r:id="R6e4f403af4584d65"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -563,6 +563,64 @@
         <x:v>3.2</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/config/excel/CfgEnemySkills.xlsx
+++ b/config/excel/CfgEnemySkills.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemySkills" sheetId="1" r:id="R6e4f403af4584d65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemySkills" sheetId="1" r:id="R14e9a971846c4fa7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +32,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -55,6 +60,21 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -62,7 +82,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -89,6 +109,14 @@
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -291,334 +319,595 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="11" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="11" t="str">
         <x:v>EnemyID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="11" t="str">
         <x:v>SkillID</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="11" t="str">
         <x:v>Priority</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="11" t="str">
         <x:v>Weight</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="11" t="str">
         <x:v>MinHealthRatio</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="11" t="str">
         <x:v>MaxHealthRatio</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="11" t="str">
         <x:v>MinDistance</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="11" t="str">
         <x:v>MaxDistance</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="12" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="12" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="12" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
+      <x:c r="D2" s="12" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="str">
+      <x:c r="E2" s="12" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="str">
+      <x:c r="F2" s="12" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="str">
+      <x:c r="G2" s="12" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="str">
+      <x:c r="H2" s="12" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="str">
+      <x:c r="I2" s="12" t="str">
         <x:v>number</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="56" customHeight="1">
-      <x:c r="A3" s="7" t="str">
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="14" t="str">
         <x:v># 敌人技能映射编号。</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="str">
+      <x:c r="B3" s="14" t="str">
         <x:v>敌人编号。</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="str">
+      <x:c r="C3" s="14" t="str">
         <x:v>战斗技能编号。</x:v>
       </x:c>
-      <x:c r="D3" s="7" t="str">
+      <x:c r="D3" s="14" t="str">
         <x:v>技能优先级；较大值优先。</x:v>
       </x:c>
-      <x:c r="E3" s="7" t="str">
+      <x:c r="E3" s="14" t="str">
         <x:v>相同优先级内随机选择权重。</x:v>
       </x:c>
-      <x:c r="F3" s="7" t="str">
+      <x:c r="F3" s="14" t="str">
         <x:v>敌人最小生命比例，含边界。</x:v>
       </x:c>
-      <x:c r="G3" s="7" t="str">
+      <x:c r="G3" s="14" t="str">
         <x:v>敌人最大生命比例，含边界。</x:v>
       </x:c>
-      <x:c r="H3" s="7" t="str">
+      <x:c r="H3" s="14" t="str">
         <x:v>最小目标距离，含边界。</x:v>
       </x:c>
-      <x:c r="I3" s="7" t="str">
+      <x:c r="I3" s="14" t="str">
         <x:v>最大目标距离，含边界。</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="36" customHeight="1">
-      <x:c r="A4" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I4" s="9" t="n">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E4" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I4" s="15" t="n">
         <x:v>2.1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="36" customHeight="1">
-      <x:c r="A5" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="n">
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I5" s="9" t="n">
+      <x:c r="D5" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I5" s="15" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="36" customHeight="1">
-      <x:c r="A6" s="8" t="n">
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="n">
+      <x:c r="B6" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="9" t="n">
+      <x:c r="D6" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F6" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="15" t="n">
         <x:v>3.2</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="36" customHeight="1">
-      <x:c r="A7" s="8" t="n">
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="n">
+      <x:c r="B7" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E7" s="8" t="n">
+      <x:c r="D7" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F7" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="9" t="n">
+      <x:c r="F7" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="15" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="H7" s="9" t="n">
+      <x:c r="H7" s="15" t="n">
         <x:v>3.2</x:v>
       </x:c>
-      <x:c r="I7" s="9" t="n">
+      <x:c r="I7" s="15" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="36" customHeight="1">
-      <x:c r="A8" s="8" t="n">
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="n">
+      <x:c r="B8" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="n">
+      <x:c r="C8" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="n">
+      <x:c r="D8" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="15" t="n">
         <x:v>3.5</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="36" customHeight="1">
-      <x:c r="A9" s="8" t="n">
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="15" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="n">
+      <x:c r="B9" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="n">
+      <x:c r="C9" s="15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="9" t="n">
+      <x:c r="D9" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="15" t="n">
         <x:v>3.2</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="36" customHeight="1">
-      <x:c r="A10" t="n">
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B10" t="n">
+      <x:c r="B10" s="15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C10" t="n">
+      <x:c r="C10" s="15" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I10" t="n">
+      <x:c r="D10" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="15" t="n">
         <x:v>2.2</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="36" customHeight="1">
-      <x:c r="A11" t="n">
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="15" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B11" t="n">
+      <x:c r="B11" s="15" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C11" t="n">
+      <x:c r="C11" s="15" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I11" t="n">
+      <x:c r="D11" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="15" t="n">
         <x:v>3.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="15" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" s="15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="15" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B13" s="15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H13" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="15" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="15" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B14" s="15" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="15" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="15" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B15" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="15" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B16" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="15" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="15" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B17" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H17" s="15" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="I17" s="15" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="15" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B18" s="15" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B19" s="15" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="15" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="15" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="15" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H20" s="15" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="I20" s="15" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
